--- a/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="675">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -656,11 +656,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -676,7 +672,8 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1337,7 +1334,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2445,17 +2442,17 @@
   <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2464,28 +2461,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="98.171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="84.1640625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4746,7 +4743,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -4772,13 +4769,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
@@ -4800,13 +4797,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4892,10 +4889,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4921,16 +4918,16 @@
         <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4979,7 +4976,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5014,10 +5011,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5040,17 +5037,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5099,7 +5096,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5114,19 +5111,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5134,14 +5131,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5160,17 +5157,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5219,7 +5216,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5234,16 +5231,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5254,14 +5251,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5280,16 +5277,16 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5339,7 +5336,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5354,30 +5351,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5403,16 +5400,16 @@
         <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5437,11 +5434,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5459,7 +5456,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>93</v>
@@ -5474,19 +5471,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5494,10 +5491,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5520,19 +5517,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5560,16 +5557,16 @@
         <v>177</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5579,7 +5576,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5603,24 +5600,24 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
@@ -5642,19 +5639,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5682,11 +5679,11 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5703,7 +5700,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5727,10 +5724,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5738,10 +5735,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5856,10 +5853,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5974,12 +5971,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6005,16 +6002,16 @@
         <v>151</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6063,7 +6060,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6084,10 +6081,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6098,10 +6095,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6216,10 +6213,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6334,12 +6331,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6365,65 +6362,65 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6444,10 +6441,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6458,10 +6455,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6487,13 +6484,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6543,7 +6540,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6564,24 +6561,24 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
+      <c r="B35" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6607,63 +6604,63 @@
         <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6684,10 +6681,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6698,10 +6695,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6727,14 +6724,14 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6783,7 +6780,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6804,10 +6801,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6818,10 +6815,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6844,19 +6841,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6905,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6926,10 +6923,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6940,10 +6937,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6969,16 +6966,16 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7027,7 +7024,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7048,28 +7045,28 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7088,19 +7085,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7128,11 +7125,11 @@
         <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7149,7 +7146,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>93</v>
@@ -7164,30 +7161,30 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7302,10 +7299,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7422,10 +7419,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7451,16 +7448,16 @@
         <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7497,7 +7494,7 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7507,7 +7504,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7528,10 +7525,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7542,13 +7539,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
@@ -7573,16 +7570,16 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7631,7 +7628,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7652,10 +7649,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7666,10 +7663,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7784,10 +7781,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7904,10 +7901,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7933,23 +7930,23 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7991,7 +7988,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8012,10 +8009,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8026,10 +8023,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8055,13 +8052,13 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8111,7 +8108,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8132,10 +8129,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8146,10 +8143,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8175,21 +8172,21 @@
         <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8231,7 +8228,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8252,10 +8249,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8266,10 +8263,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8295,14 +8292,14 @@
         <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8351,7 +8348,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8372,10 +8369,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8386,10 +8383,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8412,19 +8409,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8473,7 +8470,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8494,10 +8491,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8508,10 +8505,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8537,16 +8534,16 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8595,7 +8592,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8616,11 +8613,11 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8628,12 +8625,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8656,19 +8653,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8717,7 +8714,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8732,19 +8729,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8752,10 +8749,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8778,16 +8775,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8837,7 +8834,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8858,13 +8855,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8872,14 +8869,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8898,19 +8895,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8959,7 +8956,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8974,34 +8971,34 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AP54" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="B55" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9020,19 +9017,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9081,7 +9078,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9090,25 +9087,25 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AJ55" t="s" s="2">
+      <c r="AK55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AK55" t="s" s="2">
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9116,10 +9113,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9145,13 +9142,13 @@
         <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9201,7 +9198,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9222,13 +9219,13 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9236,10 +9233,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9262,17 +9259,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9321,7 +9318,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9336,19 +9333,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9356,10 +9353,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9382,19 +9379,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9431,17 +9428,17 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9450,7 +9447,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9459,30 +9456,30 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>444</v>
       </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
+      <c r="B59" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
@@ -9504,19 +9501,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9523,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9565,7 +9562,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9574,7 +9571,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9583,27 +9580,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9718,10 +9715,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9836,12 +9833,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9864,19 +9861,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9925,7 +9922,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9946,10 +9943,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9960,10 +9957,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9989,65 +9986,65 @@
         <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" t="s" s="2">
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y63" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y63" t="s" s="2">
+      <c r="Z63" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="Z63" t="s" s="2">
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10068,24 +10065,24 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
+      <c r="B64" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10111,14 +10108,14 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10167,7 +10164,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10188,24 +10185,24 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
+      <c r="B65" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10231,63 +10228,63 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10296,7 +10293,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10308,24 +10305,24 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
+      <c r="B66" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10351,16 +10348,16 @@
         <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10385,31 +10382,31 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10430,24 +10427,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10470,19 +10467,19 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10510,11 +10507,11 @@
         <v>155</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10531,7 +10528,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10540,7 +10537,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10555,7 +10552,7 @@
         <v>196</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10566,10 +10563,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10684,10 +10681,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10804,10 +10801,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10833,16 +10830,16 @@
         <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10891,7 +10888,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10912,10 +10909,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10926,10 +10923,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11044,10 +11041,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11164,10 +11161,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11193,16 +11190,16 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11251,7 +11248,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11272,10 +11269,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11286,10 +11283,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11315,13 +11312,13 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11371,7 +11368,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11392,10 +11389,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11406,10 +11403,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11435,14 +11432,14 @@
         <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11491,7 +11488,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11512,10 +11509,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11526,10 +11523,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11555,14 +11552,14 @@
         <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11611,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11632,10 +11629,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11646,10 +11643,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11672,19 +11669,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11733,7 +11730,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11754,10 +11751,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11768,10 +11765,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11797,16 +11794,16 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11855,7 +11852,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11876,10 +11873,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11890,14 +11887,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11916,19 +11913,19 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11957,7 +11954,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11975,7 +11972,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11993,27 +11990,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>530</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12036,19 +12033,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12097,7 +12094,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12118,10 +12115,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12132,10 +12129,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12158,16 +12155,16 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12196,11 +12193,11 @@
         <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12217,7 +12214,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12235,27 +12232,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
         <v>548</v>
       </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>549</v>
-      </c>
       <c r="B82" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12278,19 +12275,19 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12319,7 +12316,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12337,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12358,10 +12355,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12372,10 +12369,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12398,16 +12395,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12457,7 +12454,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12475,27 +12472,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>565</v>
       </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="B84" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12518,16 +12515,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12577,7 +12574,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12595,27 +12592,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12638,19 +12635,19 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12699,7 +12696,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12711,19 +12708,19 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12734,10 +12731,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12852,10 +12849,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12972,14 +12969,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13001,16 +12998,16 @@
         <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13059,7 +13056,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13094,10 +13091,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13120,13 +13117,13 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13177,7 +13174,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13186,7 +13183,7 @@
         <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>105</v>
@@ -13198,10 +13195,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13212,10 +13209,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13238,13 +13235,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13295,7 +13292,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13304,7 +13301,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13316,10 +13313,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13330,10 +13327,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13356,19 +13353,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13396,11 +13393,11 @@
         <v>177</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13417,7 +13414,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13435,13 +13432,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AN91" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13452,10 +13449,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13478,19 +13475,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13518,11 +13515,11 @@
         <v>163</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13539,7 +13536,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13557,13 +13554,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AN92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13574,10 +13571,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13600,17 +13597,17 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13659,7 +13656,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13683,7 +13680,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13694,10 +13691,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13723,10 +13720,10 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13777,7 +13774,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13798,10 +13795,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13812,10 +13809,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13838,16 +13835,16 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13897,7 +13894,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13918,10 +13915,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13932,10 +13929,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13958,16 +13955,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14017,7 +14014,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14038,24 +14035,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AN96" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>641</v>
-      </c>
       <c r="B97" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14078,19 +14075,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14139,7 +14136,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14151,19 +14148,19 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14174,10 +14171,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14292,10 +14289,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14412,14 +14409,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14441,16 +14438,16 @@
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14499,7 +14496,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14532,12 +14529,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14560,19 +14557,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14600,11 +14597,11 @@
         <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14621,7 +14618,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>93</v>
@@ -14639,27 +14636,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AM101" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>657</v>
-      </c>
       <c r="B102" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14682,19 +14679,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>661</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14719,14 +14716,14 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>663</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14743,7 +14740,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14752,7 +14749,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14761,27 +14758,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>666</v>
-      </c>
       <c r="B103" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14804,19 +14801,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>669</v>
-      </c>
       <c r="O103" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14844,11 +14841,11 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14865,7 +14862,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14874,7 +14871,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14889,7 +14886,7 @@
         <v>196</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14900,14 +14897,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14926,19 +14923,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14966,10 +14963,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14987,7 +14984,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15005,27 +15002,27 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AM104" t="s" s="2">
+      <c r="AN104" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>530</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15051,16 +15048,16 @@
         <v>83</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="N105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O105" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15109,7 +15106,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15130,10 +15127,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15144,12 +15141,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP105">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
